--- a/Equity_Portfolio_Dashboard.xlsx
+++ b/Equity_Portfolio_Dashboard.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,13 +515,13 @@
         <v>46108</v>
       </c>
       <c r="D4" t="n">
-        <v>2493</v>
+        <v>2493.5</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>14958</v>
+        <v>14961</v>
       </c>
     </row>
     <row r="5">
@@ -587,13 +587,13 @@
         <v>46251</v>
       </c>
       <c r="D7" t="n">
-        <v>3204</v>
+        <v>3203.7</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>9612</v>
+        <v>9611.099999999999</v>
       </c>
     </row>
     <row r="8">
@@ -875,13 +875,13 @@
         <v>46202</v>
       </c>
       <c r="D19" t="n">
-        <v>986</v>
+        <v>985.75</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>9860</v>
+        <v>9857.5</v>
       </c>
     </row>
     <row r="20">
@@ -899,37 +899,37 @@
         <v>46251</v>
       </c>
       <c r="D20" t="n">
-        <v>1099</v>
+        <v>1098.45</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>10990</v>
+        <v>10984.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46164</v>
+        <v>46318</v>
       </c>
       <c r="D21" t="n">
-        <v>1809</v>
+        <v>930.45</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="F21" t="n">
-        <v>9045</v>
+        <v>-18609</v>
       </c>
     </row>
     <row r="22">
@@ -944,16 +944,16 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46269</v>
+        <v>46164</v>
       </c>
       <c r="D22" t="n">
-        <v>2531</v>
+        <v>1809</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>12655</v>
+        <v>9045</v>
       </c>
     </row>
     <row r="23">
@@ -964,20 +964,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45922</v>
+        <v>46269</v>
       </c>
       <c r="D23" t="n">
-        <v>107</v>
+        <v>2531</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>1070</v>
+        <v>12655</v>
       </c>
     </row>
     <row r="24">
@@ -988,20 +988,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45929</v>
+        <v>46318</v>
       </c>
       <c r="D24" t="n">
-        <v>147</v>
+        <v>1815.43</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="F24" t="n">
-        <v>1470</v>
+        <v>-18154.3</v>
       </c>
     </row>
     <row r="25">
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45975</v>
+        <v>45922</v>
       </c>
       <c r="D25" t="n">
-        <v>107.5</v>
+        <v>107</v>
       </c>
       <c r="E25" t="n">
-        <v>-15</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>-1612.5</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="26">
@@ -1040,16 +1040,16 @@
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46017</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="n">
-        <v>106.45</v>
+        <v>147</v>
       </c>
       <c r="E26" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>-532.25</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="27">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46132</v>
+        <v>45975</v>
       </c>
       <c r="D27" t="n">
-        <v>327.5</v>
+        <v>107.5</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>-15</v>
       </c>
       <c r="F27" t="n">
-        <v>6550</v>
+        <v>-1612.5</v>
       </c>
     </row>
     <row r="28">
@@ -1084,20 +1084,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46142</v>
+        <v>46017</v>
       </c>
       <c r="D28" t="n">
-        <v>353</v>
+        <v>106.45</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="F28" t="n">
-        <v>10590</v>
+        <v>-532.25</v>
       </c>
     </row>
     <row r="29">
@@ -1112,112 +1112,112 @@
         </is>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46150</v>
+        <v>46132</v>
       </c>
       <c r="D29" t="n">
-        <v>401</v>
+        <v>327.5</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>8020</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45951</v>
+        <v>46142</v>
       </c>
       <c r="D30" t="n">
-        <v>2517</v>
+        <v>352.36</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
-        <v>12585</v>
+        <v>10570.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45989</v>
+        <v>46150</v>
       </c>
       <c r="D31" t="n">
-        <v>2900</v>
+        <v>400.8</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>8700</v>
+        <v>8016</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46062</v>
+        <v>46318</v>
       </c>
       <c r="D32" t="n">
-        <v>2975</v>
+        <v>379.55</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>-70</v>
       </c>
       <c r="F32" t="n">
-        <v>5950</v>
+        <v>-26568.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46129</v>
+        <v>46290</v>
       </c>
       <c r="D33" t="n">
-        <v>3480</v>
+        <v>199</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n">
-        <v>13920</v>
+        <v>9950</v>
       </c>
     </row>
     <row r="34">
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46157</v>
+        <v>45951</v>
       </c>
       <c r="D34" t="n">
-        <v>4015</v>
+        <v>2517</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F34" t="n">
-        <v>12045</v>
+        <v>12585</v>
       </c>
     </row>
     <row r="35">
@@ -1256,112 +1256,112 @@
         </is>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46251</v>
+        <v>45989</v>
       </c>
       <c r="D35" t="n">
-        <v>3299</v>
+        <v>2900</v>
       </c>
       <c r="E35" t="n">
-        <v>-17</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>-56083</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45922</v>
+        <v>46062</v>
       </c>
       <c r="D36" t="n">
-        <v>119</v>
+        <v>2975</v>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>1190</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45951</v>
+        <v>46129</v>
       </c>
       <c r="D37" t="n">
-        <v>128</v>
+        <v>3480</v>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>1280</v>
+        <v>13920</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45964</v>
+        <v>46157</v>
       </c>
       <c r="D38" t="n">
-        <v>139.5</v>
+        <v>4015</v>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>1395</v>
+        <v>12045</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45975</v>
+        <v>46251</v>
       </c>
       <c r="D39" t="n">
-        <v>145.5</v>
+        <v>3299</v>
       </c>
       <c r="E39" t="n">
-        <v>20</v>
+        <v>-17</v>
       </c>
       <c r="F39" t="n">
-        <v>2910</v>
+        <v>-56083</v>
       </c>
     </row>
     <row r="40">
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46017</v>
+        <v>45922</v>
       </c>
       <c r="D40" t="n">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="E40" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>4500</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="41">
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46041</v>
+        <v>45951</v>
       </c>
       <c r="D41" t="n">
-        <v>156.73</v>
+        <v>128</v>
       </c>
       <c r="E41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>3134.6</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="42">
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46094</v>
+        <v>45964</v>
       </c>
       <c r="D42" t="n">
-        <v>135</v>
+        <v>139.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-100</v>
+        <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>-13500</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="43">
@@ -1448,16 +1448,16 @@
         </is>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46132</v>
+        <v>45975</v>
       </c>
       <c r="D43" t="n">
-        <v>143</v>
+        <v>145.5</v>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>7150</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="44">
@@ -1472,16 +1472,16 @@
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46142</v>
+        <v>46017</v>
       </c>
       <c r="D44" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E44" t="n">
-        <v>-50</v>
+        <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>-6750</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="45">
@@ -1492,68 +1492,68 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46150</v>
+        <v>46041</v>
       </c>
       <c r="D45" t="n">
-        <v>857</v>
+        <v>156.73</v>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>8570</v>
+        <v>3134.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46251</v>
+        <v>46094</v>
       </c>
       <c r="D46" t="n">
-        <v>1809</v>
+        <v>135</v>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>-100</v>
       </c>
       <c r="F46" t="n">
-        <v>9045</v>
+        <v>-13500</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46269</v>
+        <v>46132</v>
       </c>
       <c r="D47" t="n">
-        <v>1980</v>
+        <v>143</v>
       </c>
       <c r="E47" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>9900</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="48">
@@ -1564,20 +1564,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45852</v>
+        <v>46142</v>
       </c>
       <c r="D48" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E48" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F48" t="n">
-        <v>6500</v>
+        <v>-6750</v>
       </c>
     </row>
     <row r="49">
@@ -1588,20 +1588,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45856</v>
+        <v>46150</v>
       </c>
       <c r="D49" t="n">
-        <v>146</v>
+        <v>856.6</v>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>7300</v>
+        <v>8566</v>
       </c>
     </row>
     <row r="50">
@@ -1612,68 +1612,68 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45922</v>
+        <v>46318</v>
       </c>
       <c r="D50" t="n">
-        <v>217</v>
+        <v>782.16</v>
       </c>
       <c r="E50" t="n">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="F50" t="n">
-        <v>6510</v>
+        <v>-7821.599999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45951</v>
+        <v>46251</v>
       </c>
       <c r="D51" t="n">
-        <v>253</v>
+        <v>1809</v>
       </c>
       <c r="E51" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>5060</v>
+        <v>9045</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45975</v>
+        <v>46269</v>
       </c>
       <c r="D52" t="n">
-        <v>314</v>
+        <v>1980</v>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F52" t="n">
-        <v>3140</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="53">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46027</v>
+        <v>45852</v>
       </c>
       <c r="D53" t="n">
-        <v>354</v>
+        <v>130</v>
       </c>
       <c r="E53" t="n">
-        <v>-150</v>
+        <v>50</v>
       </c>
       <c r="F53" t="n">
-        <v>-53100</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="54">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46041</v>
+        <v>45856</v>
       </c>
       <c r="D54" t="n">
-        <v>439</v>
+        <v>146</v>
       </c>
       <c r="E54" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F54" t="n">
-        <v>17560</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="55">
@@ -1736,16 +1736,16 @@
         </is>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46043</v>
+        <v>45922</v>
       </c>
       <c r="D55" t="n">
-        <v>375</v>
+        <v>217</v>
       </c>
       <c r="E55" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F55" t="n">
-        <v>18750</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="56">
@@ -1760,16 +1760,16 @@
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46043</v>
+        <v>45951</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="E56" t="n">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="57">
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46202</v>
+        <v>45975</v>
       </c>
       <c r="D57" t="n">
-        <v>188.5</v>
+        <v>314</v>
       </c>
       <c r="E57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F57" t="n">
-        <v>4712.5</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="58">
@@ -1808,16 +1808,16 @@
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46248</v>
+        <v>46027</v>
       </c>
       <c r="D58" t="n">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="E58" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="F58" t="n">
-        <v>-29500</v>
+        <v>-53100</v>
       </c>
     </row>
     <row r="59">
@@ -1828,20 +1828,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46269</v>
+        <v>46041</v>
       </c>
       <c r="D59" t="n">
-        <v>857</v>
+        <v>439</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F59" t="n">
-        <v>4285</v>
+        <v>17560</v>
       </c>
     </row>
     <row r="60">
@@ -1852,20 +1852,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45951</v>
+        <v>46043</v>
       </c>
       <c r="D60" t="n">
-        <v>339.5</v>
+        <v>375</v>
       </c>
       <c r="E60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>3395</v>
+        <v>18750</v>
       </c>
     </row>
     <row r="61">
@@ -1876,20 +1876,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45975</v>
+        <v>46043</v>
       </c>
       <c r="D61" t="n">
-        <v>300.5</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>-6</v>
+        <v>400</v>
       </c>
       <c r="F61" t="n">
-        <v>-1803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1900,20 +1900,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46017</v>
+        <v>46202</v>
       </c>
       <c r="D62" t="n">
-        <v>283</v>
+        <v>188.45</v>
       </c>
       <c r="E62" t="n">
-        <v>-4</v>
+        <v>25</v>
       </c>
       <c r="F62" t="n">
-        <v>-1132</v>
+        <v>4711.25</v>
       </c>
     </row>
     <row r="63">
@@ -1924,20 +1924,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45845</v>
+        <v>46248</v>
       </c>
       <c r="D63" t="n">
-        <v>540</v>
+        <v>295</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>-100</v>
       </c>
       <c r="F63" t="n">
-        <v>5400</v>
+        <v>-29500</v>
       </c>
     </row>
     <row r="64">
@@ -1948,20 +1948,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45856</v>
+        <v>46248</v>
       </c>
       <c r="D64" t="n">
-        <v>586</v>
+        <v>250</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>-400</v>
       </c>
       <c r="F64" t="n">
-        <v>2930</v>
+        <v>-100000</v>
       </c>
     </row>
     <row r="65">
@@ -1972,20 +1972,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45866</v>
+        <v>46304</v>
       </c>
       <c r="D65" t="n">
-        <v>675</v>
+        <v>365.4</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F65" t="n">
-        <v>3375</v>
+        <v>27405</v>
       </c>
     </row>
     <row r="66">
@@ -1996,20 +1996,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45887</v>
+        <v>46269</v>
       </c>
       <c r="D66" t="n">
-        <v>626</v>
+        <v>856.9</v>
       </c>
       <c r="E66" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="F66" t="n">
-        <v>-12520</v>
+        <v>4284.5</v>
       </c>
     </row>
     <row r="67">
@@ -2020,20 +2020,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45953</v>
+        <v>46252</v>
       </c>
       <c r="D67" t="n">
-        <v>535</v>
+        <v>941.6</v>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F67" t="n">
-        <v>2675</v>
+        <v>18832</v>
       </c>
     </row>
     <row r="68">
@@ -2044,140 +2044,140 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45971</v>
+        <v>46318</v>
       </c>
       <c r="D68" t="n">
-        <v>637.5</v>
+        <v>710.33</v>
       </c>
       <c r="E68" t="n">
-        <v>-5</v>
+        <v>-25</v>
       </c>
       <c r="F68" t="n">
-        <v>-3187.5</v>
+        <v>-17758.25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46142</v>
+        <v>45951</v>
       </c>
       <c r="D69" t="n">
-        <v>4475</v>
+        <v>339.5</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F69" t="n">
-        <v>8950</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45832</v>
+        <v>45975</v>
       </c>
       <c r="D70" t="n">
-        <v>1975</v>
+        <v>300.5</v>
       </c>
       <c r="E70" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="F70" t="n">
-        <v>9875</v>
+        <v>-1803</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45887</v>
+        <v>46017</v>
       </c>
       <c r="D71" t="n">
-        <v>2005</v>
+        <v>283</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="F71" t="n">
-        <v>10025</v>
+        <v>-1132</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45897</v>
+        <v>45845</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="E72" t="n">
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46108</v>
+        <v>45856</v>
       </c>
       <c r="D73" t="n">
-        <v>762</v>
+        <v>586</v>
       </c>
       <c r="E73" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
-        <v>-15240</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="74">
@@ -2188,20 +2188,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46150</v>
+        <v>45866</v>
       </c>
       <c r="D74" t="n">
-        <v>148</v>
+        <v>675</v>
       </c>
       <c r="E74" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
-        <v>7400</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="75">
@@ -2212,20 +2212,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46167</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="n">
-        <v>162</v>
+        <v>626</v>
       </c>
       <c r="E75" t="n">
-        <v>50</v>
+        <v>-20</v>
       </c>
       <c r="F75" t="n">
-        <v>8100</v>
+        <v>-12520</v>
       </c>
     </row>
     <row r="76">
@@ -2236,20 +2236,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46178</v>
+        <v>45953</v>
       </c>
       <c r="D76" t="n">
-        <v>187</v>
+        <v>535</v>
       </c>
       <c r="E76" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
-        <v>9350</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="77">
@@ -2260,260 +2260,260 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46248</v>
+        <v>45971</v>
       </c>
       <c r="D77" t="n">
-        <v>223</v>
+        <v>637.5</v>
       </c>
       <c r="E77" t="n">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="F77" t="n">
-        <v>6690</v>
+        <v>-3187.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46006</v>
+        <v>46252</v>
       </c>
       <c r="D78" t="n">
-        <v>380</v>
+        <v>1465.4</v>
       </c>
       <c r="E78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>3800</v>
+        <v>21981</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46013</v>
+        <v>46318</v>
       </c>
       <c r="D79" t="n">
-        <v>405</v>
+        <v>1207.73</v>
       </c>
       <c r="E79" t="n">
-        <v>10</v>
+        <v>-15</v>
       </c>
       <c r="F79" t="n">
-        <v>4050</v>
+        <v>-18115.95</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46017</v>
+        <v>46142</v>
       </c>
       <c r="D80" t="n">
-        <v>474.5</v>
+        <v>4475</v>
       </c>
       <c r="E80" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>9490</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46027</v>
+        <v>46318</v>
       </c>
       <c r="D81" t="n">
-        <v>561</v>
+        <v>3571.65</v>
       </c>
       <c r="E81" t="n">
-        <v>30</v>
+        <v>-2</v>
       </c>
       <c r="F81" t="n">
-        <v>16830</v>
+        <v>-7143.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46052</v>
+        <v>45832</v>
       </c>
       <c r="D82" t="n">
-        <v>688.3</v>
+        <v>1975</v>
       </c>
       <c r="E82" t="n">
-        <v>-50</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>-34415</v>
+        <v>9875</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46059</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="n">
-        <v>576.7</v>
+        <v>2005</v>
       </c>
       <c r="E83" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>-11534</v>
+        <v>10025</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46071</v>
+        <v>45897</v>
       </c>
       <c r="D84" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46094</v>
+        <v>46108</v>
       </c>
       <c r="D85" t="n">
-        <v>117.6</v>
+        <v>762</v>
       </c>
       <c r="E85" t="n">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F85" t="n">
-        <v>-5880</v>
+        <v>-15240</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46202</v>
+        <v>46150</v>
       </c>
       <c r="D86" t="n">
-        <v>520</v>
+        <v>148.12</v>
       </c>
       <c r="E86" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>7800</v>
+        <v>7406</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46266</v>
+        <v>46167</v>
       </c>
       <c r="D87" t="n">
-        <v>470</v>
+        <v>162</v>
       </c>
       <c r="E87" t="n">
-        <v>-15</v>
+        <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>-7050</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="88">
@@ -2524,20 +2524,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46132</v>
+        <v>46178</v>
       </c>
       <c r="D88" t="n">
-        <v>240</v>
+        <v>187.23</v>
       </c>
       <c r="E88" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>4800</v>
+        <v>9361.5</v>
       </c>
     </row>
     <row r="89">
@@ -2548,20 +2548,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46255</v>
+        <v>46248</v>
       </c>
       <c r="D89" t="n">
-        <v>291</v>
+        <v>222.81</v>
       </c>
       <c r="E89" t="n">
         <v>30</v>
       </c>
       <c r="F89" t="n">
-        <v>8730</v>
+        <v>6684.3</v>
       </c>
     </row>
     <row r="90">
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46027</v>
+        <v>46304</v>
       </c>
       <c r="D90" t="n">
-        <v>508</v>
+        <v>258.5</v>
       </c>
       <c r="E90" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F90" t="n">
-        <v>5080</v>
+        <v>7755</v>
       </c>
     </row>
     <row r="91">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46059</v>
+        <v>46006</v>
       </c>
       <c r="D91" t="n">
-        <v>547.5</v>
+        <v>380</v>
       </c>
       <c r="E91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>10950</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="92">
@@ -2620,20 +2620,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46066</v>
+        <v>46013</v>
       </c>
       <c r="D92" t="n">
-        <v>587</v>
+        <v>405</v>
       </c>
       <c r="E92" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
-        <v>17610</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="93">
@@ -2644,116 +2644,116 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46094</v>
+        <v>46017</v>
       </c>
       <c r="D93" t="n">
-        <v>414</v>
+        <v>474.5</v>
       </c>
       <c r="E93" t="n">
-        <v>-60</v>
+        <v>20</v>
       </c>
       <c r="F93" t="n">
-        <v>-24840</v>
+        <v>9490</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46269</v>
+        <v>46027</v>
       </c>
       <c r="D94" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="E94" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F94" t="n">
-        <v>8500</v>
+        <v>16830</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46251</v>
+        <v>46052</v>
       </c>
       <c r="D95" t="n">
-        <v>189</v>
+        <v>688.3</v>
       </c>
       <c r="E95" t="n">
-        <v>25</v>
+        <v>-50</v>
       </c>
       <c r="F95" t="n">
-        <v>4725</v>
+        <v>-34415</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46129</v>
+        <v>46059</v>
       </c>
       <c r="D96" t="n">
-        <v>968.5</v>
+        <v>576.7</v>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="F96" t="n">
-        <v>4842.5</v>
+        <v>-11534</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46178</v>
+        <v>46071</v>
       </c>
       <c r="D97" t="n">
-        <v>811</v>
+        <v>144</v>
       </c>
       <c r="E97" t="n">
-        <v>-5</v>
+        <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>-4055</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="98">
@@ -2764,68 +2764,68 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="D98" t="n">
-        <v>1072.5</v>
+        <v>117.6</v>
       </c>
       <c r="E98" t="n">
-        <v>5</v>
+        <v>-50</v>
       </c>
       <c r="F98" t="n">
-        <v>5362.5</v>
+        <v>-5880</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46150</v>
+        <v>46202</v>
       </c>
       <c r="D99" t="n">
-        <v>1263</v>
+        <v>520</v>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F99" t="n">
-        <v>12630</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46202</v>
+        <v>46266</v>
       </c>
       <c r="D100" t="n">
-        <v>1493</v>
+        <v>470</v>
       </c>
       <c r="E100" t="n">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="F100" t="n">
-        <v>7465</v>
+        <v>-7050</v>
       </c>
     </row>
     <row r="101">
@@ -2836,68 +2836,68 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46255</v>
+        <v>46132</v>
       </c>
       <c r="D101" t="n">
-        <v>1802</v>
+        <v>240</v>
       </c>
       <c r="E101" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F101" t="n">
-        <v>9010</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46136</v>
+        <v>46255</v>
       </c>
       <c r="D102" t="n">
-        <v>2294</v>
+        <v>291.2</v>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F102" t="n">
-        <v>11470</v>
+        <v>8736</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46269</v>
+        <v>46318</v>
       </c>
       <c r="D103" t="n">
-        <v>732</v>
+        <v>234.5</v>
       </c>
       <c r="E103" t="n">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F103" t="n">
-        <v>7320</v>
+        <v>-11725</v>
       </c>
     </row>
     <row r="104">
@@ -2908,20 +2908,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46006</v>
+        <v>46027</v>
       </c>
       <c r="D104" t="n">
-        <v>120</v>
+        <v>508</v>
       </c>
       <c r="E104" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F104" t="n">
-        <v>2400</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="105">
@@ -2932,20 +2932,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="D105" t="n">
-        <v>130.8</v>
+        <v>547.5</v>
       </c>
       <c r="E105" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F105" t="n">
-        <v>3924</v>
+        <v>10950</v>
       </c>
     </row>
     <row r="106">
@@ -2956,92 +2956,92 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46094</v>
+        <v>46066</v>
       </c>
       <c r="D106" t="n">
-        <v>115</v>
+        <v>587</v>
       </c>
       <c r="E106" t="n">
-        <v>-50</v>
+        <v>30</v>
       </c>
       <c r="F106" t="n">
-        <v>-5750</v>
+        <v>17610</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45951</v>
+        <v>46094</v>
       </c>
       <c r="D107" t="n">
-        <v>1029</v>
+        <v>414</v>
       </c>
       <c r="E107" t="n">
-        <v>5</v>
+        <v>-60</v>
       </c>
       <c r="F107" t="n">
-        <v>5145</v>
+        <v>-24840</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46094</v>
+        <v>46262</v>
       </c>
       <c r="D108" t="n">
-        <v>680</v>
+        <v>604</v>
       </c>
       <c r="E108" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="F108" t="n">
-        <v>-3400</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46269</v>
+        <v>46283</v>
       </c>
       <c r="D109" t="n">
-        <v>1036</v>
+        <v>676.8</v>
       </c>
       <c r="E109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F109" t="n">
-        <v>10360</v>
+        <v>10152</v>
       </c>
     </row>
     <row r="110">
@@ -3052,116 +3052,116 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45964</v>
+        <v>46304</v>
       </c>
       <c r="D110" t="n">
-        <v>168.5</v>
+        <v>804</v>
       </c>
       <c r="E110" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F110" t="n">
-        <v>1348</v>
+        <v>12060</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46017</v>
+        <v>46269</v>
       </c>
       <c r="D111" t="n">
-        <v>145.9</v>
+        <v>424.65</v>
       </c>
       <c r="E111" t="n">
-        <v>-8</v>
+        <v>20</v>
       </c>
       <c r="F111" t="n">
-        <v>-1167.2</v>
+        <v>8493</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46066</v>
+        <v>46251</v>
       </c>
       <c r="D112" t="n">
-        <v>185.73</v>
+        <v>189</v>
       </c>
       <c r="E112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F112" t="n">
-        <v>1857.3</v>
+        <v>4725</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46073</v>
+        <v>46129</v>
       </c>
       <c r="D113" t="n">
-        <v>191.5</v>
+        <v>968.5</v>
       </c>
       <c r="E113" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F113" t="n">
-        <v>3830</v>
+        <v>4842.5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46087</v>
+        <v>46178</v>
       </c>
       <c r="D114" t="n">
-        <v>210</v>
+        <v>811</v>
       </c>
       <c r="E114" t="n">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="F114" t="n">
-        <v>6300</v>
+        <v>-4055</v>
       </c>
     </row>
     <row r="115">
@@ -3172,20 +3172,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46142</v>
+        <v>46080</v>
       </c>
       <c r="D115" t="n">
-        <v>167</v>
+        <v>1072.5</v>
       </c>
       <c r="E115" t="n">
-        <v>-60</v>
+        <v>5</v>
       </c>
       <c r="F115" t="n">
-        <v>-10020</v>
+        <v>5362.5</v>
       </c>
     </row>
     <row r="116">
@@ -3196,20 +3196,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45839</v>
+        <v>46150</v>
       </c>
       <c r="D116" t="n">
-        <v>801</v>
+        <v>1263.25</v>
       </c>
       <c r="E116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F116" t="n">
-        <v>4005</v>
+        <v>12632.5</v>
       </c>
     </row>
     <row r="117">
@@ -3220,20 +3220,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45861</v>
+        <v>46202</v>
       </c>
       <c r="D117" t="n">
-        <v>848</v>
+        <v>1493.05</v>
       </c>
       <c r="E117" t="n">
         <v>5</v>
       </c>
       <c r="F117" t="n">
-        <v>4240</v>
+        <v>7465.25</v>
       </c>
     </row>
     <row r="118">
@@ -3244,20 +3244,20 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45936</v>
+        <v>46255</v>
       </c>
       <c r="D118" t="n">
-        <v>874</v>
+        <v>1802</v>
       </c>
       <c r="E118" t="n">
         <v>5</v>
       </c>
       <c r="F118" t="n">
-        <v>4370</v>
+        <v>9010</v>
       </c>
     </row>
     <row r="119">
@@ -3268,140 +3268,140 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45953</v>
+        <v>46304</v>
       </c>
       <c r="D119" t="n">
-        <v>942</v>
+        <v>2038.3</v>
       </c>
       <c r="E119" t="n">
         <v>5</v>
       </c>
       <c r="F119" t="n">
-        <v>4710</v>
+        <v>10191.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46142</v>
+        <v>46136</v>
       </c>
       <c r="D120" t="n">
-        <v>1007</v>
+        <v>2293.7</v>
       </c>
       <c r="E120" t="n">
         <v>5</v>
       </c>
       <c r="F120" t="n">
-        <v>5035</v>
+        <v>11468.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46255</v>
+        <v>46318</v>
       </c>
       <c r="D121" t="n">
-        <v>1247</v>
+        <v>1899.68</v>
       </c>
       <c r="E121" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F121" t="n">
-        <v>6235</v>
+        <v>-9498.4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45945</v>
+        <v>46006</v>
       </c>
       <c r="D122" t="n">
-        <v>4898</v>
+        <v>120</v>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F122" t="n">
-        <v>14694</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45982</v>
+        <v>46066</v>
       </c>
       <c r="D123" t="n">
-        <v>5880</v>
+        <v>130.8</v>
       </c>
       <c r="E123" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F123" t="n">
-        <v>17640</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46251</v>
+        <v>46094</v>
       </c>
       <c r="D124" t="n">
-        <v>8179</v>
+        <v>115</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>-50</v>
       </c>
       <c r="F124" t="n">
-        <v>32716</v>
+        <v>-5750</v>
       </c>
     </row>
     <row r="125">
@@ -3412,92 +3412,92 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46178</v>
+        <v>45951</v>
       </c>
       <c r="D125" t="n">
-        <v>1970</v>
+        <v>1029</v>
       </c>
       <c r="E125" t="n">
         <v>5</v>
       </c>
       <c r="F125" t="n">
-        <v>9850</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46227</v>
+        <v>46094</v>
       </c>
       <c r="D126" t="n">
-        <v>1700</v>
+        <v>680</v>
       </c>
       <c r="E126" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="F126" t="n">
-        <v>17000</v>
+        <v>-3400</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46248</v>
+        <v>46269</v>
       </c>
       <c r="D127" t="n">
-        <v>1865</v>
+        <v>1036.14</v>
       </c>
       <c r="E127" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F127" t="n">
-        <v>13055</v>
+        <v>10361.4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46255</v>
+        <v>46318</v>
       </c>
       <c r="D128" t="n">
-        <v>2047</v>
+        <v>924.75</v>
       </c>
       <c r="E128" t="n">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="F128" t="n">
-        <v>16376</v>
+        <v>-9247.5</v>
       </c>
     </row>
     <row r="129">
@@ -3508,20 +3508,20 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NRBBEARING</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46167</v>
+        <v>45964</v>
       </c>
       <c r="D129" t="n">
-        <v>387</v>
+        <v>168.5</v>
       </c>
       <c r="E129" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F129" t="n">
-        <v>3870</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="130">
@@ -3532,20 +3532,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NRBBEARING</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46255</v>
+        <v>46017</v>
       </c>
       <c r="D130" t="n">
-        <v>487</v>
+        <v>145.9</v>
       </c>
       <c r="E130" t="n">
-        <v>30</v>
+        <v>-8</v>
       </c>
       <c r="F130" t="n">
-        <v>14610</v>
+        <v>-1167.2</v>
       </c>
     </row>
     <row r="131">
@@ -3556,20 +3556,20 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NRBBEARING</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46269</v>
+        <v>46066</v>
       </c>
       <c r="D131" t="n">
-        <v>447</v>
+        <v>185.73</v>
       </c>
       <c r="E131" t="n">
-        <v>-40</v>
+        <v>10</v>
       </c>
       <c r="F131" t="n">
-        <v>-17880</v>
+        <v>1857.3</v>
       </c>
     </row>
     <row r="132">
@@ -3580,20 +3580,20 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NSE:APOLLO</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45832</v>
+        <v>46073</v>
       </c>
       <c r="D132" t="n">
-        <v>202</v>
+        <v>191.5</v>
       </c>
       <c r="E132" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F132" t="n">
-        <v>5050</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="133">
@@ -3604,20 +3604,20 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NSE:APOLLO</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45856</v>
+        <v>46087</v>
       </c>
       <c r="D133" t="n">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="E133" t="n">
-        <v>-25</v>
+        <v>30</v>
       </c>
       <c r="F133" t="n">
-        <v>-4425</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="134">
@@ -3628,68 +3628,68 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NSE:APOLLO</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46017</v>
+        <v>46142</v>
       </c>
       <c r="D134" t="n">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="E134" t="n">
-        <v>5</v>
+        <v>-60</v>
       </c>
       <c r="F134" t="n">
-        <v>1340</v>
+        <v>-10020</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NSE:APOLLO</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46094</v>
+        <v>46269</v>
       </c>
       <c r="D135" t="n">
-        <v>208</v>
+        <v>731.65</v>
       </c>
       <c r="E135" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="F135" t="n">
-        <v>-1040</v>
+        <v>7316.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NSE:APOLLO</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46132</v>
+        <v>46318</v>
       </c>
       <c r="D136" t="n">
-        <v>290</v>
+        <v>567.77</v>
       </c>
       <c r="E136" t="n">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="F136" t="n">
-        <v>8700</v>
+        <v>-5677.7</v>
       </c>
     </row>
     <row r="137">
@@ -3700,20 +3700,20 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NSE:APOLLO</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46178</v>
+        <v>45839</v>
       </c>
       <c r="D137" t="n">
-        <v>422.5</v>
+        <v>801.5</v>
       </c>
       <c r="E137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F137" t="n">
-        <v>4225</v>
+        <v>4007.5</v>
       </c>
     </row>
     <row r="138">
@@ -3724,20 +3724,20 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NSE:BDL</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45832</v>
+        <v>45861</v>
       </c>
       <c r="D138" t="n">
-        <v>1864</v>
+        <v>848</v>
       </c>
       <c r="E138" t="n">
         <v>5</v>
       </c>
       <c r="F138" t="n">
-        <v>9320</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="139">
@@ -3748,20 +3748,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NSE:BDL</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45856</v>
+        <v>45936</v>
       </c>
       <c r="D139" t="n">
-        <v>1700</v>
+        <v>874</v>
       </c>
       <c r="E139" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="F139" t="n">
-        <v>-8500</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="140">
@@ -3772,20 +3772,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NSE:BEL</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45832</v>
+        <v>45953</v>
       </c>
       <c r="D140" t="n">
-        <v>418</v>
+        <v>942</v>
       </c>
       <c r="E140" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F140" t="n">
-        <v>6270</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="141">
@@ -3796,68 +3796,68 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NSE:BEL</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46248</v>
+        <v>46142</v>
       </c>
       <c r="D141" t="n">
-        <v>410</v>
+        <v>1007</v>
       </c>
       <c r="E141" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="F141" t="n">
-        <v>-6150</v>
+        <v>5035</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NSE:CCL</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45982</v>
+        <v>46255</v>
       </c>
       <c r="D142" t="n">
-        <v>1002</v>
+        <v>1247.2</v>
       </c>
       <c r="E142" t="n">
         <v>5</v>
       </c>
       <c r="F142" t="n">
-        <v>5010</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NSE:CCL</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46129</v>
+        <v>46304</v>
       </c>
       <c r="D143" t="n">
-        <v>1089</v>
+        <v>1042.66</v>
       </c>
       <c r="E143" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
       <c r="F143" t="n">
-        <v>5445</v>
+        <v>-31279.8</v>
       </c>
     </row>
     <row r="144">
@@ -3868,20 +3868,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NSE:CCL</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46142</v>
+        <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>1136</v>
+        <v>4898</v>
       </c>
       <c r="E144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F144" t="n">
-        <v>5680</v>
+        <v>14694</v>
       </c>
     </row>
     <row r="145">
@@ -3892,20 +3892,20 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NSE:CUB</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46003</v>
+        <v>45982</v>
       </c>
       <c r="D145" t="n">
-        <v>275</v>
+        <v>5880</v>
       </c>
       <c r="E145" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F145" t="n">
-        <v>1375</v>
+        <v>17640</v>
       </c>
     </row>
     <row r="146">
@@ -3916,20 +3916,20 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NSE:CUB</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46108</v>
+        <v>46251</v>
       </c>
       <c r="D146" t="n">
-        <v>248</v>
+        <v>8178.5</v>
       </c>
       <c r="E146" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F146" t="n">
-        <v>1240</v>
+        <v>32714</v>
       </c>
     </row>
     <row r="147">
@@ -3940,20 +3940,20 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NSE:CUB</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46185</v>
+        <v>46178</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>1970</v>
       </c>
       <c r="E147" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>9850</v>
       </c>
     </row>
     <row r="148">
@@ -3964,44 +3964,44 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NSE:MCX</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46157</v>
+        <v>46318</v>
       </c>
       <c r="D148" t="n">
-        <v>3392</v>
+        <v>1637.04</v>
       </c>
       <c r="E148" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F148" t="n">
-        <v>16960</v>
+        <v>-8185.2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NSE:MCX</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46178</v>
+        <v>46227</v>
       </c>
       <c r="D149" t="n">
-        <v>2803</v>
+        <v>1700</v>
       </c>
       <c r="E149" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="F149" t="n">
-        <v>-14015</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="150">
@@ -4012,20 +4012,20 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NSE:RBA</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46202</v>
+        <v>46248</v>
       </c>
       <c r="D150" t="n">
-        <v>80</v>
+        <v>1865</v>
       </c>
       <c r="E150" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="F150" t="n">
-        <v>8000</v>
+        <v>13055</v>
       </c>
     </row>
     <row r="151">
@@ -4036,20 +4036,20 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NSE:RBA</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46227</v>
+        <v>46255</v>
       </c>
       <c r="D151" t="n">
-        <v>65</v>
+        <v>2047.2</v>
       </c>
       <c r="E151" t="n">
-        <v>-100</v>
+        <v>8</v>
       </c>
       <c r="F151" t="n">
-        <v>-6500</v>
+        <v>16377.6</v>
       </c>
     </row>
     <row r="152">
@@ -4060,20 +4060,20 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NSE:RBA</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46239</v>
+        <v>46283</v>
       </c>
       <c r="D152" t="n">
-        <v>90</v>
+        <v>1900</v>
       </c>
       <c r="E152" t="n">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="F152" t="n">
-        <v>9000</v>
+        <v>-47500</v>
       </c>
     </row>
     <row r="153">
@@ -4084,20 +4084,20 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NSE:RBA</t>
+          <t>NRBBEARING</t>
         </is>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46255</v>
+        <v>46167</v>
       </c>
       <c r="D153" t="n">
-        <v>104.5</v>
+        <v>387</v>
       </c>
       <c r="E153" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F153" t="n">
-        <v>10450</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="154">
@@ -4108,20 +4108,20 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NSE:SFL</t>
+          <t>NRBBEARING</t>
         </is>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46164</v>
+        <v>46255</v>
       </c>
       <c r="D154" t="n">
-        <v>639.5</v>
+        <v>487</v>
       </c>
       <c r="E154" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F154" t="n">
-        <v>6395</v>
+        <v>14610</v>
       </c>
     </row>
     <row r="155">
@@ -4132,20 +4132,20 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NSE:SFL</t>
+          <t>NRBBEARING</t>
         </is>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46227</v>
+        <v>46269</v>
       </c>
       <c r="D155" t="n">
-        <v>763</v>
+        <v>447</v>
       </c>
       <c r="E155" t="n">
-        <v>20</v>
+        <v>-40</v>
       </c>
       <c r="F155" t="n">
-        <v>15260</v>
+        <v>-17880</v>
       </c>
     </row>
     <row r="156">
@@ -4156,164 +4156,164 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NSE:SFL</t>
+          <t>NSE:APOLLO</t>
         </is>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46255</v>
+        <v>45832</v>
       </c>
       <c r="D156" t="n">
-        <v>667</v>
+        <v>202</v>
       </c>
       <c r="E156" t="n">
-        <v>-30</v>
+        <v>25</v>
       </c>
       <c r="F156" t="n">
-        <v>-20010</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>NSE:APOLLO</t>
         </is>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45982</v>
+        <v>45856</v>
       </c>
       <c r="D157" t="n">
-        <v>7540</v>
+        <v>177</v>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>-25</v>
       </c>
       <c r="F157" t="n">
-        <v>15080</v>
+        <v>-4425</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>NSE:APOLLO</t>
         </is>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46129</v>
+        <v>46017</v>
       </c>
       <c r="D158" t="n">
-        <v>8194</v>
+        <v>268</v>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F158" t="n">
-        <v>16388</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>NSE:APOLLO</t>
         </is>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46157</v>
+        <v>46094</v>
       </c>
       <c r="D159" t="n">
-        <v>9168</v>
+        <v>208</v>
       </c>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="F159" t="n">
-        <v>18336</v>
+        <v>-1040</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>NSE:APOLLO</t>
         </is>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46269</v>
+        <v>46132</v>
       </c>
       <c r="D160" t="n">
-        <v>8358</v>
+        <v>289.5</v>
       </c>
       <c r="E160" t="n">
-        <v>-6</v>
+        <v>30</v>
       </c>
       <c r="F160" t="n">
-        <v>-50148</v>
+        <v>8685</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>NSE:APOLLO</t>
         </is>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46129</v>
+        <v>46178</v>
       </c>
       <c r="D161" t="n">
-        <v>318</v>
+        <v>422.5</v>
       </c>
       <c r="E161" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F161" t="n">
-        <v>9540</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>NSE:BDL</t>
         </is>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46245</v>
+        <v>45832</v>
       </c>
       <c r="D162" t="n">
-        <v>267</v>
+        <v>1864</v>
       </c>
       <c r="E162" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
       <c r="F162" t="n">
-        <v>-8010</v>
+        <v>9320</v>
       </c>
     </row>
     <row r="163">
@@ -4324,20 +4324,20 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PRECWIRE</t>
+          <t>NSE:BDL</t>
         </is>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45936</v>
+        <v>45856</v>
       </c>
       <c r="D163" t="n">
-        <v>207.5</v>
+        <v>1700</v>
       </c>
       <c r="E163" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="F163" t="n">
-        <v>2075</v>
+        <v>-8500</v>
       </c>
     </row>
     <row r="164">
@@ -4348,20 +4348,20 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PRECWIRE</t>
+          <t>NSE:BEL</t>
         </is>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45975</v>
+        <v>45832</v>
       </c>
       <c r="D164" t="n">
-        <v>271</v>
+        <v>418</v>
       </c>
       <c r="E164" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F164" t="n">
-        <v>2710</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="165">
@@ -4372,44 +4372,44 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PRECWIRE</t>
+          <t>NSE:BEL</t>
         </is>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46080</v>
+        <v>46248</v>
       </c>
       <c r="D165" t="n">
-        <v>311.73</v>
+        <v>410</v>
       </c>
       <c r="E165" t="n">
-        <v>20</v>
+        <v>-15</v>
       </c>
       <c r="F165" t="n">
-        <v>6234.6</v>
+        <v>-6150</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PRECWIRE</t>
+          <t>NSE:CCL</t>
         </is>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46142</v>
+        <v>45982</v>
       </c>
       <c r="D166" t="n">
-        <v>423</v>
+        <v>1002</v>
       </c>
       <c r="E166" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F166" t="n">
-        <v>8460</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="167">
@@ -4420,20 +4420,20 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>NSE:CCL</t>
         </is>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46251</v>
+        <v>46129</v>
       </c>
       <c r="D167" t="n">
-        <v>795</v>
+        <v>1088.65</v>
       </c>
       <c r="E167" t="n">
         <v>5</v>
       </c>
       <c r="F167" t="n">
-        <v>3975</v>
+        <v>5443.25</v>
       </c>
     </row>
     <row r="168">
@@ -4444,20 +4444,20 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>NSE:CCL</t>
         </is>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45964</v>
+        <v>46142</v>
       </c>
       <c r="D168" t="n">
-        <v>2928</v>
+        <v>1135.6</v>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F168" t="n">
-        <v>5856</v>
+        <v>5678</v>
       </c>
     </row>
     <row r="169">
@@ -4468,20 +4468,20 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>NSE:CCL</t>
         </is>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46129</v>
+        <v>46318</v>
       </c>
       <c r="D169" t="n">
-        <v>3099</v>
+        <v>902.37</v>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>-15</v>
       </c>
       <c r="F169" t="n">
-        <v>9297</v>
+        <v>-13535.55</v>
       </c>
     </row>
     <row r="170">
@@ -4492,92 +4492,92 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>NSE:CUB</t>
         </is>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46251</v>
+        <v>46003</v>
       </c>
       <c r="D170" t="n">
-        <v>3452</v>
+        <v>274.65</v>
       </c>
       <c r="E170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F170" t="n">
-        <v>13808</v>
+        <v>1373.25</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>RAJRATAN</t>
+          <t>NSE:CUB</t>
         </is>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45964</v>
+        <v>46108</v>
       </c>
       <c r="D171" t="n">
-        <v>444</v>
+        <v>247.75</v>
       </c>
       <c r="E171" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F171" t="n">
-        <v>1332</v>
+        <v>1238.75</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>RAJRATAN</t>
+          <t>NSE:CUB</t>
         </is>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46027</v>
+        <v>46185</v>
       </c>
       <c r="D172" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F172" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RAJRATAN</t>
+          <t>NSE:MCX</t>
         </is>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46094</v>
+        <v>46157</v>
       </c>
       <c r="D173" t="n">
-        <v>373</v>
+        <v>3392</v>
       </c>
       <c r="E173" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="F173" t="n">
-        <v>-2984</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="174">
@@ -4588,20 +4588,20 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>NSE:MCX</t>
         </is>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46251</v>
+        <v>46178</v>
       </c>
       <c r="D174" t="n">
-        <v>520</v>
+        <v>2803</v>
       </c>
       <c r="E174" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="F174" t="n">
-        <v>5200</v>
+        <v>-14015</v>
       </c>
     </row>
     <row r="175">
@@ -4612,20 +4612,20 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>NSE:RBA</t>
         </is>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46164</v>
+        <v>46202</v>
       </c>
       <c r="D175" t="n">
-        <v>501</v>
+        <v>80</v>
       </c>
       <c r="E175" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F175" t="n">
-        <v>5010</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="176">
@@ -4636,20 +4636,20 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>NSE:RBA</t>
         </is>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46178</v>
+        <v>46227</v>
       </c>
       <c r="D176" t="n">
-        <v>542</v>
+        <v>65</v>
       </c>
       <c r="E176" t="n">
-        <v>10</v>
+        <v>-100</v>
       </c>
       <c r="F176" t="n">
-        <v>5420</v>
+        <v>-6500</v>
       </c>
     </row>
     <row r="177">
@@ -4660,20 +4660,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>NSE:RBA</t>
         </is>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="D177" t="n">
-        <v>605</v>
+        <v>90</v>
       </c>
       <c r="E177" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F177" t="n">
-        <v>12100</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="178">
@@ -4684,116 +4684,116 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>NSE:RBA</t>
         </is>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="D178" t="n">
-        <v>821</v>
+        <v>104.42</v>
       </c>
       <c r="E178" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F178" t="n">
-        <v>8210</v>
+        <v>10442</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SIRCA</t>
+          <t>NSE:RBA</t>
         </is>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45852</v>
+        <v>46283</v>
       </c>
       <c r="D179" t="n">
-        <v>415</v>
+        <v>94.91</v>
       </c>
       <c r="E179" t="n">
-        <v>20</v>
+        <v>-200</v>
       </c>
       <c r="F179" t="n">
-        <v>8300</v>
+        <v>-18982</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SIRCA</t>
+          <t>NSE:SFL</t>
         </is>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45903</v>
+        <v>46164</v>
       </c>
       <c r="D180" t="n">
-        <v>462</v>
+        <v>639.5</v>
       </c>
       <c r="E180" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F180" t="n">
-        <v>9240</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SIRCA</t>
+          <t>NSE:SFL</t>
         </is>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45945</v>
+        <v>46227</v>
       </c>
       <c r="D181" t="n">
-        <v>503</v>
+        <v>763</v>
       </c>
       <c r="E181" t="n">
         <v>20</v>
       </c>
       <c r="F181" t="n">
-        <v>10060</v>
+        <v>15260</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SIRCA</t>
+          <t>NSE:SFL</t>
         </is>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46202</v>
+        <v>46255</v>
       </c>
       <c r="D182" t="n">
-        <v>407</v>
+        <v>667</v>
       </c>
       <c r="E182" t="n">
-        <v>-60</v>
+        <v>-30</v>
       </c>
       <c r="F182" t="n">
-        <v>-24420</v>
+        <v>-20010</v>
       </c>
     </row>
     <row r="183">
@@ -4804,20 +4804,20 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>NSE:UNIMECH</t>
         </is>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45951</v>
+        <v>46251</v>
       </c>
       <c r="D183" t="n">
-        <v>39.2</v>
+        <v>1494</v>
       </c>
       <c r="E183" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F183" t="n">
-        <v>3920</v>
+        <v>11952</v>
       </c>
     </row>
     <row r="184">
@@ -4828,20 +4828,20 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>NSE:UNIMECH</t>
         </is>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46041</v>
+        <v>46252</v>
       </c>
       <c r="D184" t="n">
-        <v>45</v>
+        <v>1596.7</v>
       </c>
       <c r="E184" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F184" t="n">
-        <v>4500</v>
+        <v>9580.200000000001</v>
       </c>
     </row>
     <row r="185">
@@ -4852,20 +4852,20 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>NSE:UNIMECH</t>
         </is>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46052</v>
+        <v>46290</v>
       </c>
       <c r="D185" t="n">
-        <v>37.6</v>
+        <v>1671.37</v>
       </c>
       <c r="E185" t="n">
-        <v>-200</v>
+        <v>6</v>
       </c>
       <c r="F185" t="n">
-        <v>-7520</v>
+        <v>10028.22</v>
       </c>
     </row>
     <row r="186">
@@ -4876,44 +4876,44 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>NSE:UNIMECH</t>
         </is>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46132</v>
+        <v>46318</v>
       </c>
       <c r="D186" t="n">
-        <v>39.4</v>
+        <v>1488.93</v>
       </c>
       <c r="E186" t="n">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F186" t="n">
-        <v>3940</v>
+        <v>-29778.6</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46188</v>
+        <v>45982</v>
       </c>
       <c r="D187" t="n">
-        <v>48</v>
+        <v>7540</v>
       </c>
       <c r="E187" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F187" t="n">
-        <v>2400</v>
+        <v>15080</v>
       </c>
     </row>
     <row r="188">
@@ -4924,20 +4924,20 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45964</v>
+        <v>46129</v>
       </c>
       <c r="D188" t="n">
-        <v>792</v>
+        <v>8194</v>
       </c>
       <c r="E188" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F188" t="n">
-        <v>4752</v>
+        <v>16388</v>
       </c>
     </row>
     <row r="189">
@@ -4948,20 +4948,20 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46062</v>
+        <v>46157</v>
       </c>
       <c r="D189" t="n">
-        <v>877</v>
+        <v>9168</v>
       </c>
       <c r="E189" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F189" t="n">
-        <v>4385</v>
+        <v>18336</v>
       </c>
     </row>
     <row r="190">
@@ -4972,20 +4972,20 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46129</v>
+        <v>46269</v>
       </c>
       <c r="D190" t="n">
-        <v>981</v>
+        <v>8358</v>
       </c>
       <c r="E190" t="n">
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="F190" t="n">
-        <v>8829</v>
+        <v>-50148</v>
       </c>
     </row>
     <row r="191">
@@ -4996,20 +4996,20 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46202</v>
+        <v>46129</v>
       </c>
       <c r="D191" t="n">
-        <v>1366</v>
+        <v>318</v>
       </c>
       <c r="E191" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F191" t="n">
-        <v>13660</v>
+        <v>9540</v>
       </c>
     </row>
     <row r="192">
@@ -5020,116 +5020,116 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="D192" t="n">
-        <v>1468</v>
+        <v>267</v>
       </c>
       <c r="E192" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
       <c r="F192" t="n">
-        <v>14680</v>
+        <v>-8010</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PRECWIRE</t>
         </is>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46066</v>
+        <v>45936</v>
       </c>
       <c r="D193" t="n">
-        <v>416.5</v>
+        <v>207.41</v>
       </c>
       <c r="E193" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F193" t="n">
-        <v>2082.5</v>
+        <v>2074.1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PRECWIRE</t>
         </is>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46066</v>
+        <v>45975</v>
       </c>
       <c r="D194" t="n">
-        <v>416.5</v>
+        <v>271</v>
       </c>
       <c r="E194" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F194" t="n">
-        <v>2082.5</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PRECWIRE</t>
         </is>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="D195" t="n">
-        <v>442</v>
+        <v>311.73</v>
       </c>
       <c r="E195" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F195" t="n">
-        <v>6630</v>
+        <v>6234.6</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PRECWIRE</t>
         </is>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46073</v>
+        <v>46142</v>
       </c>
       <c r="D196" t="n">
-        <v>442</v>
+        <v>422.75</v>
       </c>
       <c r="E196" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F196" t="n">
-        <v>6630</v>
+        <v>8455</v>
       </c>
     </row>
     <row r="197">
@@ -5140,20 +5140,20 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46132</v>
+        <v>46251</v>
       </c>
       <c r="D197" t="n">
-        <v>519</v>
+        <v>794.5</v>
       </c>
       <c r="E197" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F197" t="n">
-        <v>2595</v>
+        <v>5561.5</v>
       </c>
     </row>
     <row r="198">
@@ -5164,20 +5164,20 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46132</v>
+        <v>46318</v>
       </c>
       <c r="D198" t="n">
-        <v>519</v>
+        <v>622.05</v>
       </c>
       <c r="E198" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="F198" t="n">
-        <v>2595</v>
+        <v>-4354.349999999999</v>
       </c>
     </row>
     <row r="199">
@@ -5188,20 +5188,20 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46248</v>
+        <v>45964</v>
       </c>
       <c r="D199" t="n">
-        <v>742</v>
+        <v>2928</v>
       </c>
       <c r="E199" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F199" t="n">
-        <v>6678</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="200">
@@ -5212,116 +5212,116 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46248</v>
+        <v>46129</v>
       </c>
       <c r="D200" t="n">
-        <v>742</v>
+        <v>3099</v>
       </c>
       <c r="E200" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F200" t="n">
-        <v>6678</v>
+        <v>9297</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SATELLITE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>NSE:UNIMECH</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="C201" s="1" t="n">
         <v>46251</v>
       </c>
       <c r="D201" t="n">
-        <v>1494</v>
+        <v>3451.65</v>
       </c>
       <c r="E201" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F201" t="n">
-        <v>11952</v>
+        <v>13806.6</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>RAJRATAN</t>
         </is>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45903</v>
+        <v>45964</v>
       </c>
       <c r="D202" t="n">
-        <v>1288</v>
+        <v>444</v>
       </c>
       <c r="E202" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F202" t="n">
-        <v>12880</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>RAJRATAN</t>
         </is>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46157</v>
+        <v>46027</v>
       </c>
       <c r="D203" t="n">
-        <v>1131</v>
+        <v>480</v>
       </c>
       <c r="E203" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="F203" t="n">
-        <v>-11310</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>SATELLITE</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>RAJRATAN</t>
         </is>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46178</v>
+        <v>46094</v>
       </c>
       <c r="D204" t="n">
-        <v>521.6</v>
+        <v>373</v>
       </c>
       <c r="E204" t="n">
-        <v>10</v>
+        <v>-8</v>
       </c>
       <c r="F204" t="n">
-        <v>5216</v>
+        <v>-2984</v>
       </c>
     </row>
     <row r="205">
@@ -5332,19 +5332,739 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D205" t="n">
+        <v>519.55</v>
+      </c>
+      <c r="E205" t="n">
+        <v>10</v>
+      </c>
+      <c r="F205" t="n">
+        <v>5195.5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="D206" t="n">
+        <v>501</v>
+      </c>
+      <c r="E206" t="n">
+        <v>10</v>
+      </c>
+      <c r="F206" t="n">
+        <v>5010</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="D207" t="n">
+        <v>542</v>
+      </c>
+      <c r="E207" t="n">
+        <v>10</v>
+      </c>
+      <c r="F207" t="n">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="D208" t="n">
+        <v>604.8</v>
+      </c>
+      <c r="E208" t="n">
+        <v>20</v>
+      </c>
+      <c r="F208" t="n">
+        <v>12096</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D209" t="n">
+        <v>820.85</v>
+      </c>
+      <c r="E209" t="n">
+        <v>10</v>
+      </c>
+      <c r="F209" t="n">
+        <v>8208.5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1022.65</v>
+      </c>
+      <c r="E210" t="n">
+        <v>10</v>
+      </c>
+      <c r="F210" t="n">
+        <v>10226.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SIRCA</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="D211" t="n">
+        <v>415</v>
+      </c>
+      <c r="E211" t="n">
+        <v>20</v>
+      </c>
+      <c r="F211" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SIRCA</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="D212" t="n">
+        <v>462</v>
+      </c>
+      <c r="E212" t="n">
+        <v>20</v>
+      </c>
+      <c r="F212" t="n">
+        <v>9240</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SIRCA</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="D213" t="n">
+        <v>503</v>
+      </c>
+      <c r="E213" t="n">
+        <v>20</v>
+      </c>
+      <c r="F213" t="n">
+        <v>10060</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SIRCA</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="D214" t="n">
+        <v>407</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-60</v>
+      </c>
+      <c r="F214" t="n">
+        <v>-24420</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="D215" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E215" t="n">
+        <v>100</v>
+      </c>
+      <c r="F215" t="n">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="D216" t="n">
+        <v>45</v>
+      </c>
+      <c r="E216" t="n">
+        <v>100</v>
+      </c>
+      <c r="F216" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="D217" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="E217" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F217" t="n">
+        <v>-7520</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D218" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="E218" t="n">
+        <v>100</v>
+      </c>
+      <c r="F218" t="n">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="D219" t="n">
+        <v>48</v>
+      </c>
+      <c r="E219" t="n">
+        <v>50</v>
+      </c>
+      <c r="F219" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="D220" t="n">
+        <v>792</v>
+      </c>
+      <c r="E220" t="n">
+        <v>6</v>
+      </c>
+      <c r="F220" t="n">
+        <v>4752</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="D221" t="n">
+        <v>877</v>
+      </c>
+      <c r="E221" t="n">
+        <v>5</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4385</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="D222" t="n">
+        <v>980.6</v>
+      </c>
+      <c r="E222" t="n">
+        <v>9</v>
+      </c>
+      <c r="F222" t="n">
+        <v>8825.4</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1366.6</v>
+      </c>
+      <c r="E223" t="n">
+        <v>10</v>
+      </c>
+      <c r="F223" t="n">
+        <v>13666</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1467.5</v>
+      </c>
+      <c r="E224" t="n">
+        <v>10</v>
+      </c>
+      <c r="F224" t="n">
+        <v>14675</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="D225" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="E225" t="n">
+        <v>10</v>
+      </c>
+      <c r="F225" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D226" t="n">
+        <v>442</v>
+      </c>
+      <c r="E226" t="n">
+        <v>30</v>
+      </c>
+      <c r="F226" t="n">
+        <v>13260</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D227" t="n">
+        <v>518.97</v>
+      </c>
+      <c r="E227" t="n">
+        <v>10</v>
+      </c>
+      <c r="F227" t="n">
+        <v>5189.700000000001</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D228" t="n">
+        <v>742</v>
+      </c>
+      <c r="E228" t="n">
+        <v>18</v>
+      </c>
+      <c r="F228" t="n">
+        <v>13356</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="D229" t="n">
+        <v>794.1</v>
+      </c>
+      <c r="E229" t="n">
+        <v>17</v>
+      </c>
+      <c r="F229" t="n">
+        <v>13499.7</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>TEGA</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D230" t="n">
+        <v>2090</v>
+      </c>
+      <c r="E230" t="n">
+        <v>5</v>
+      </c>
+      <c r="F230" t="n">
+        <v>10450</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>TEGA</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1695.9</v>
+      </c>
+      <c r="E231" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F231" t="n">
+        <v>-8479.5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1288</v>
+      </c>
+      <c r="E232" t="n">
+        <v>10</v>
+      </c>
+      <c r="F232" t="n">
+        <v>12880</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1131</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F233" t="n">
+        <v>-11310</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
           <t>VBL</t>
         </is>
       </c>
-      <c r="C205" s="1" t="n">
+      <c r="C234" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="D234" t="n">
+        <v>521.6</v>
+      </c>
+      <c r="E234" t="n">
+        <v>10</v>
+      </c>
+      <c r="F234" t="n">
+        <v>5216</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="n">
         <v>46245</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D235" t="n">
         <v>444</v>
       </c>
-      <c r="E205" t="n">
+      <c r="E235" t="n">
         <v>-10</v>
       </c>
-      <c r="F205" t="n">
+      <c r="F235" t="n">
         <v>-4440</v>
       </c>
     </row>
